--- a/data/Jugadores/Demo.xlsx
+++ b/data/Jugadores/Demo.xlsx
@@ -457,8 +457,12 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="B11" s="2">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
@@ -548,8 +552,12 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
+      <c r="B24" s="2">
+        <v>4</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
